--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123516989</v>
+        <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövängesberget, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540903</v>
+        <v>540819</v>
       </c>
       <c r="R2" t="n">
-        <v>6725777</v>
+        <v>6725899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516989</t>
+          <t>https://artportalen.se/Sighting/136797791</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517071</v>
+        <v>123516989</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -820,31 +820,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fetbergsta, Fetbergsta, Dlr</t>
+          <t>Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540989</v>
+        <v>540903</v>
       </c>
       <c r="R3" t="n">
-        <v>6725705</v>
+        <v>6725777</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,34 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517071</t>
+          <t>https://artportalen.se/Sighting/123516989</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123516716</v>
+        <v>123517071</v>
       </c>
       <c r="B4" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,37 +915,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Fetbergsta, Fetbergsta, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540891</v>
+        <v>540989</v>
       </c>
       <c r="R4" t="n">
-        <v>6725826</v>
+        <v>6725705</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,59 +1022,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516716</t>
+          <t>https://artportalen.se/Sighting/123517071</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123520458</v>
+        <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540656</v>
+        <v>540815</v>
       </c>
       <c r="R5" t="n">
-        <v>6725616</v>
+        <v>6725904</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,73 +1123,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520458</t>
+          <t>https://artportalen.se/Sighting/136797792</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123522769</v>
+        <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövängesberget, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540648</v>
+        <v>540846</v>
       </c>
       <c r="R6" t="n">
-        <v>6725604</v>
+        <v>6725883</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1205,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,65 +1235,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522769</t>
+          <t>https://artportalen.se/Sighting/136797802</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123536374</v>
+        <v>123516716</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540690</v>
+        <v>540891</v>
       </c>
       <c r="R7" t="n">
-        <v>6725591</v>
+        <v>6725826</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,14 +1320,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,65 +1347,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536374</t>
+          <t>https://artportalen.se/Sighting/123516716</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123536375</v>
+        <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>92543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540900</v>
+        <v>540819</v>
       </c>
       <c r="R8" t="n">
-        <v>6725595</v>
+        <v>6725899</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,17 +1429,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,27 +1459,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536375</t>
+          <t>https://artportalen.se/Sighting/136797790</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123519345</v>
+        <v>123520458</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,34 +1487,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540870</v>
+        <v>540656</v>
       </c>
       <c r="R9" t="n">
-        <v>6725553</v>
+        <v>6725616</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1549,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,27 +1576,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519345</t>
+          <t>https://artportalen.se/Sighting/123520458</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123521183</v>
+        <v>123522769</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,23 +1626,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540644</v>
+        <v>540648</v>
       </c>
       <c r="R10" t="n">
-        <v>6725466</v>
+        <v>6725604</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,27 +1696,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123521183</t>
+          <t>https://artportalen.se/Sighting/123522769</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123522280</v>
+        <v>123536374</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,37 +1724,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540658</v>
+        <v>540690</v>
       </c>
       <c r="R11" t="n">
-        <v>6725589</v>
+        <v>6725591</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,19 +1781,14 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:32</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,27 +1803,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522280</t>
+          <t>https://artportalen.se/Sighting/123536374</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123522434</v>
+        <v>123536375</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,46 +1831,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540849</v>
+        <v>540900</v>
       </c>
       <c r="R12" t="n">
-        <v>6725650</v>
+        <v>6725595</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,19 +1888,14 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:36</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,27 +1910,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522434</t>
+          <t>https://artportalen.se/Sighting/123536375</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123536373</v>
+        <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,37 +1938,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540711</v>
+        <v>540594</v>
       </c>
       <c r="R13" t="n">
-        <v>6725627</v>
+        <v>6725818</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,12 +2001,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,27 +2031,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536373</t>
+          <t>https://artportalen.se/Sighting/136797798</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123536398</v>
+        <v>123519345</v>
       </c>
       <c r="B14" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,37 +2059,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540795</v>
+        <v>540870</v>
       </c>
       <c r="R14" t="n">
-        <v>6725884</v>
+        <v>6725553</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,9 +2116,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,27 +2143,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536398</t>
+          <t>https://artportalen.se/Sighting/123519345</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123536399</v>
+        <v>123521183</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,37 +2171,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540782</v>
+        <v>540644</v>
       </c>
       <c r="R15" t="n">
-        <v>6725856</v>
+        <v>6725466</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,9 +2236,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,27 +2263,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536399</t>
+          <t>https://artportalen.se/Sighting/123521183</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123536400</v>
+        <v>123522280</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,37 +2291,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540689</v>
+        <v>540658</v>
       </c>
       <c r="R16" t="n">
-        <v>6725644</v>
+        <v>6725589</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,9 +2348,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,27 +2375,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536400</t>
+          <t>https://artportalen.se/Sighting/123522280</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123536401</v>
+        <v>123522434</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,37 +2403,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540749</v>
+        <v>540849</v>
       </c>
       <c r="R17" t="n">
-        <v>6725619</v>
+        <v>6725650</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2420,9 +2469,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,27 +2496,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536401</t>
+          <t>https://artportalen.se/Sighting/123522434</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123522834</v>
+        <v>123536373</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,46 +2524,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540753</v>
+        <v>540711</v>
       </c>
       <c r="R18" t="n">
-        <v>6725675</v>
+        <v>6725627</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,55 +2581,44 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522834</t>
+          <t>https://artportalen.se/Sighting/123536373</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524035</v>
+        <v>136797794</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>4777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,34 +2626,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövängesberget, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540681</v>
+        <v>540777</v>
       </c>
       <c r="R19" t="n">
-        <v>6725657</v>
+        <v>6725882</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,22 +2685,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,27 +2715,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524035</t>
+          <t>https://artportalen.se/Sighting/136797794</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123536379</v>
+        <v>123536398</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,21 +2743,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540765</v>
+        <v>540795</v>
       </c>
       <c r="R20" t="n">
-        <v>6725845</v>
+        <v>6725884</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2784,16 +2828,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536379</t>
+          <t>https://artportalen.se/Sighting/123536398</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123536380</v>
+        <v>123536399</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2845,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2869,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540902</v>
+        <v>540782</v>
       </c>
       <c r="R21" t="n">
-        <v>6725636</v>
+        <v>6725856</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,16 +2930,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536380</t>
+          <t>https://artportalen.se/Sighting/123536399</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123536381</v>
+        <v>123536400</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,21 +2947,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2971,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540784</v>
+        <v>540689</v>
       </c>
       <c r="R22" t="n">
-        <v>6725679</v>
+        <v>6725644</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2988,16 +3032,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536381</t>
+          <t>https://artportalen.se/Sighting/123536400</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123536382</v>
+        <v>123536401</v>
       </c>
       <c r="B23" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,21 +3049,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3073,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540839</v>
+        <v>540749</v>
       </c>
       <c r="R23" t="n">
-        <v>6725797</v>
+        <v>6725619</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3090,16 +3134,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536382</t>
+          <t>https://artportalen.se/Sighting/123536401</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123536383</v>
+        <v>136797795</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>5182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3107,37 +3151,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540863</v>
+        <v>540777</v>
       </c>
       <c r="R24" t="n">
-        <v>6725784</v>
+        <v>6725882</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,12 +3210,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,27 +3240,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536383</t>
+          <t>https://artportalen.se/Sighting/136797795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123536384</v>
+        <v>136797799</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>5182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,37 +3268,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540893</v>
+        <v>540805</v>
       </c>
       <c r="R25" t="n">
-        <v>6725829</v>
+        <v>6725854</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,12 +3327,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,74 +3357,70 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536384</t>
+          <t>https://artportalen.se/Sighting/136797799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123516435</v>
+        <v>136797801</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>5182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540869</v>
+        <v>540846</v>
       </c>
       <c r="R26" t="n">
-        <v>6725826</v>
+        <v>6725883</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,22 +3444,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,74 +3479,74 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516435</t>
+          <t>https://artportalen.se/Sighting/136797801</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123516535</v>
+        <v>123522834</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540893</v>
+        <v>540753</v>
       </c>
       <c r="R27" t="n">
-        <v>6725825</v>
+        <v>6725675</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3500,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3510,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,75 +3594,72 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516535</t>
+          <t>https://artportalen.se/Sighting/123522834</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123516680</v>
+        <v>123524035</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540879</v>
+        <v>540681</v>
       </c>
       <c r="R28" t="n">
-        <v>6725801</v>
+        <v>6725657</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3626,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,74 +3713,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516680</t>
+          <t>https://artportalen.se/Sighting/123524035</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123516664</v>
+        <v>123536379</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540876</v>
+        <v>540765</v>
       </c>
       <c r="R29" t="n">
-        <v>6725782</v>
+        <v>6725845</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3735,19 +3798,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,74 +3815,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123516664</t>
+          <t>https://artportalen.se/Sighting/123536379</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123519080</v>
+        <v>123536380</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540907</v>
+        <v>540902</v>
       </c>
       <c r="R30" t="n">
-        <v>6725775</v>
+        <v>6725636</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3856,19 +3900,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,74 +3917,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519080</t>
+          <t>https://artportalen.se/Sighting/123536380</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123517012</v>
+        <v>123536381</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540910</v>
+        <v>540784</v>
       </c>
       <c r="R31" t="n">
-        <v>6725780</v>
+        <v>6725679</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3977,19 +4002,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,65 +4019,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517012</t>
+          <t>https://artportalen.se/Sighting/123536381</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123517057</v>
+        <v>123536382</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540898</v>
+        <v>540839</v>
       </c>
       <c r="R32" t="n">
-        <v>6725795</v>
+        <v>6725797</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4089,19 +4104,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4116,74 +4121,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517057</t>
+          <t>https://artportalen.se/Sighting/123536382</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123517062</v>
+        <v>123536383</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540910</v>
+        <v>540863</v>
       </c>
       <c r="R33" t="n">
-        <v>6725783</v>
+        <v>6725784</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4210,19 +4206,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4237,65 +4223,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517062</t>
+          <t>https://artportalen.se/Sighting/123536383</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123517084</v>
+        <v>123536384</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540903</v>
+        <v>540893</v>
       </c>
       <c r="R34" t="n">
-        <v>6725777</v>
+        <v>6725829</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4322,19 +4308,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4349,74 +4325,70 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517084</t>
+          <t>https://artportalen.se/Sighting/123536384</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123517431</v>
+        <v>136797797</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fetbergsta, Fetbergsta, Dlr</t>
+          <t>Lövängsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540988</v>
+        <v>540606</v>
       </c>
       <c r="R35" t="n">
-        <v>6725670</v>
+        <v>6725730</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4440,22 +4412,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4470,24 +4447,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517431</t>
+          <t>https://artportalen.se/Sighting/136797797</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123517760</v>
+        <v>123516435</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4517,12 +4494,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4531,13 +4508,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540914</v>
+        <v>540869</v>
       </c>
       <c r="R36" t="n">
-        <v>6725695</v>
+        <v>6725826</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,7 +4543,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4576,7 +4553,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4591,24 +4568,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123517760</t>
+          <t>https://artportalen.se/Sighting/123516435</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123518992</v>
+        <v>123516535</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4638,7 +4615,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4652,13 +4629,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540941</v>
+        <v>540893</v>
       </c>
       <c r="R37" t="n">
-        <v>6725637</v>
+        <v>6725825</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4687,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4697,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4723,13 +4700,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123518992</t>
+          <t>https://artportalen.se/Sighting/123516535</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123519125</v>
+        <v>123516680</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4759,12 +4736,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4773,13 +4745,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540942</v>
+        <v>540879</v>
       </c>
       <c r="R38" t="n">
-        <v>6725634</v>
+        <v>6725801</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,7 +4780,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4818,7 +4790,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,24 +4805,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519125</t>
+          <t>https://artportalen.se/Sighting/123516680</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123519174</v>
+        <v>123516664</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4880,12 +4852,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4894,13 +4866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540935</v>
+        <v>540876</v>
       </c>
       <c r="R39" t="n">
-        <v>6725587</v>
+        <v>6725782</v>
       </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4929,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4954,24 +4926,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519174</t>
+          <t>https://artportalen.se/Sighting/123516664</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123519227</v>
+        <v>123519080</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5001,12 +4973,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5015,13 +4987,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540899</v>
+        <v>540907</v>
       </c>
       <c r="R40" t="n">
-        <v>6725574</v>
+        <v>6725775</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5050,7 +5022,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,7 +5032,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,24 +5047,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519227</t>
+          <t>https://artportalen.se/Sighting/123519080</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123519883</v>
+        <v>123517012</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5122,7 +5094,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5136,13 +5108,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540816</v>
+        <v>540910</v>
       </c>
       <c r="R41" t="n">
-        <v>6725577</v>
+        <v>6725780</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5171,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5207,13 +5179,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519883</t>
+          <t>https://artportalen.se/Sighting/123517012</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123519901</v>
+        <v>123517057</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5248,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540839</v>
+        <v>540898</v>
       </c>
       <c r="R42" t="n">
-        <v>6725538</v>
+        <v>6725795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5283,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5293,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,13 +5291,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123519901</t>
+          <t>https://artportalen.se/Sighting/123517057</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123520485</v>
+        <v>123517062</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5355,12 +5327,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5369,13 +5341,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540793</v>
+        <v>540910</v>
       </c>
       <c r="R43" t="n">
-        <v>6725563</v>
+        <v>6725783</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5404,7 +5376,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5414,7 +5386,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,24 +5401,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520485</t>
+          <t>https://artportalen.se/Sighting/123517062</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123520333</v>
+        <v>123517084</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5474,29 +5446,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540691</v>
+        <v>540903</v>
       </c>
       <c r="R44" t="n">
-        <v>6725594</v>
+        <v>6725777</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5525,7 +5488,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5498,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,24 +5513,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520333</t>
+          <t>https://artportalen.se/Sighting/123517084</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123520658</v>
+        <v>123517431</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5597,7 +5560,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5607,17 +5570,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Fetbergsta, Fetbergsta, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540705</v>
+        <v>540988</v>
       </c>
       <c r="R45" t="n">
-        <v>6725507</v>
+        <v>6725670</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5646,7 +5609,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5656,7 +5619,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,24 +5634,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520658</t>
+          <t>https://artportalen.se/Sighting/123517431</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123520715</v>
+        <v>123517760</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5718,7 +5681,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5732,13 +5695,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540685</v>
+        <v>540914</v>
       </c>
       <c r="R46" t="n">
-        <v>6725524</v>
+        <v>6725695</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5767,7 +5730,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5777,7 +5740,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5803,13 +5766,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520715</t>
+          <t>https://artportalen.se/Sighting/123517760</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123522273</v>
+        <v>123518992</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5837,20 +5800,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540615</v>
+        <v>540941</v>
       </c>
       <c r="R47" t="n">
-        <v>6725540</v>
+        <v>6725637</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5879,7 +5851,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5889,7 +5861,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,24 +5876,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522273</t>
+          <t>https://artportalen.se/Sighting/123518992</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123522668</v>
+        <v>123519125</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5951,7 +5923,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5965,13 +5937,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540661</v>
+        <v>540942</v>
       </c>
       <c r="R48" t="n">
-        <v>6725569</v>
+        <v>6725634</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6000,7 +5972,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6010,7 +5982,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6036,13 +6008,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522668</t>
+          <t>https://artportalen.se/Sighting/123519125</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123522862</v>
+        <v>123519174</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6072,7 +6044,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6086,13 +6058,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540667</v>
+        <v>540935</v>
       </c>
       <c r="R49" t="n">
-        <v>6725615</v>
+        <v>6725587</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6121,7 +6093,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +6103,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6157,13 +6129,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123522862</t>
+          <t>https://artportalen.se/Sighting/123519174</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123524057</v>
+        <v>123519227</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6193,12 +6165,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6207,13 +6179,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540679</v>
+        <v>540899</v>
       </c>
       <c r="R50" t="n">
-        <v>6725630</v>
+        <v>6725574</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6242,7 +6214,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6252,7 +6224,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6267,24 +6239,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524057</t>
+          <t>https://artportalen.se/Sighting/123519227</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123523049</v>
+        <v>123519883</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6314,12 +6286,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6333,13 +6300,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540700</v>
+        <v>540816</v>
       </c>
       <c r="R51" t="n">
-        <v>6725648</v>
+        <v>6725577</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6368,7 +6335,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6378,7 +6345,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6404,13 +6371,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123523049</t>
+          <t>https://artportalen.se/Sighting/123519883</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123523976</v>
+        <v>123519901</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6438,34 +6405,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540767</v>
+        <v>540839</v>
       </c>
       <c r="R52" t="n">
-        <v>6725683</v>
+        <v>6725538</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6494,7 +6447,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6504,7 +6457,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6519,24 +6472,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123523976</t>
+          <t>https://artportalen.se/Sighting/123519901</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123536385</v>
+        <v>123520485</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6564,20 +6517,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540817</v>
+        <v>540793</v>
       </c>
       <c r="R53" t="n">
-        <v>6725903</v>
+        <v>6725563</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6604,9 +6566,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6621,24 +6593,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536385</t>
+          <t>https://artportalen.se/Sighting/123520485</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123536386</v>
+        <v>123520333</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6666,20 +6638,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540780</v>
+        <v>540691</v>
       </c>
       <c r="R54" t="n">
-        <v>6725838</v>
+        <v>6725594</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6706,9 +6687,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6723,24 +6714,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536386</t>
+          <t>https://artportalen.se/Sighting/123520333</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123536387</v>
+        <v>123520658</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6768,20 +6759,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540700</v>
+        <v>540705</v>
       </c>
       <c r="R55" t="n">
-        <v>6725691</v>
+        <v>6725507</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6808,9 +6808,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6825,24 +6835,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536387</t>
+          <t>https://artportalen.se/Sighting/123520658</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123536388</v>
+        <v>123520715</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6870,20 +6880,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540702</v>
+        <v>540685</v>
       </c>
       <c r="R56" t="n">
-        <v>6725668</v>
+        <v>6725524</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6910,9 +6929,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6927,24 +6956,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536388</t>
+          <t>https://artportalen.se/Sighting/123520715</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123536389</v>
+        <v>123522273</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6975,17 +7004,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540672</v>
+        <v>540615</v>
       </c>
       <c r="R57" t="n">
-        <v>6725589</v>
+        <v>6725540</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7012,9 +7041,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7029,24 +7068,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536389</t>
+          <t>https://artportalen.se/Sighting/123522273</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123536390</v>
+        <v>123522668</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7074,20 +7113,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540710</v>
+        <v>540661</v>
       </c>
       <c r="R58" t="n">
-        <v>6725572</v>
+        <v>6725569</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7114,9 +7162,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7131,24 +7189,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536390</t>
+          <t>https://artportalen.se/Sighting/123522668</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123536391</v>
+        <v>123522862</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7176,20 +7234,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540831</v>
+        <v>540667</v>
       </c>
       <c r="R59" t="n">
-        <v>6725795</v>
+        <v>6725615</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7216,9 +7283,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7233,24 +7310,24 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536391</t>
+          <t>https://artportalen.se/Sighting/123522862</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123536392</v>
+        <v>123524057</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7278,20 +7355,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540891</v>
+        <v>540679</v>
       </c>
       <c r="R60" t="n">
-        <v>6725807</v>
+        <v>6725630</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7318,9 +7404,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7335,24 +7431,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536392</t>
+          <t>https://artportalen.se/Sighting/123524057</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123536393</v>
+        <v>123523049</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7380,20 +7476,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540883</v>
+        <v>540700</v>
       </c>
       <c r="R61" t="n">
-        <v>6725845</v>
+        <v>6725648</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7420,9 +7530,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7437,24 +7557,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536393</t>
+          <t>https://artportalen.se/Sighting/123523049</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123536395</v>
+        <v>123523976</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7482,17 +7602,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sundborn, Dlr</t>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540903</v>
+        <v>540767</v>
       </c>
       <c r="R62" t="n">
-        <v>6725820</v>
+        <v>6725683</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7522,9 +7656,19 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7539,84 +7683,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536395</t>
+          <t>https://artportalen.se/Sighting/123523976</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123520461</v>
+        <v>123536385</v>
       </c>
       <c r="B63" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540752</v>
+        <v>540817</v>
       </c>
       <c r="R63" t="n">
-        <v>6725524</v>
+        <v>6725903</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7643,19 +7768,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7670,49 +7785,49 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520461</t>
+          <t>https://artportalen.se/Sighting/123536385</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123536377</v>
+        <v>123536386</v>
       </c>
       <c r="B64" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7722,10 +7837,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540675</v>
+        <v>540780</v>
       </c>
       <c r="R64" t="n">
-        <v>6725546</v>
+        <v>6725838</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7783,54 +7898,54 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536377</t>
+          <t>https://artportalen.se/Sighting/123536386</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123520468</v>
+        <v>123536387</v>
       </c>
       <c r="B65" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540656</v>
+        <v>540700</v>
       </c>
       <c r="R65" t="n">
-        <v>6725616</v>
+        <v>6725691</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7857,19 +7972,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7884,69 +7989,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520468</t>
+          <t>https://artportalen.se/Sighting/123536387</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123520537</v>
+        <v>123536388</v>
       </c>
       <c r="B66" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540657</v>
+        <v>540702</v>
       </c>
       <c r="R66" t="n">
-        <v>6725618</v>
+        <v>6725668</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7973,107 +8074,82 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123520537</t>
+          <t>https://artportalen.se/Sighting/123536388</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123522966</v>
+        <v>123536389</v>
       </c>
       <c r="B67" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lövängesberget, Lövängesberget, Dlr</t>
+          <t>Sundborn, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540693</v>
+        <v>540672</v>
       </c>
       <c r="R67" t="n">
-        <v>6725637</v>
+        <v>6725589</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8100,19 +8176,9 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8127,16 +8193,1961 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536389</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123536390</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>540710</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6725572</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536390</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123536391</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>540831</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6725795</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536391</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123536392</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>540891</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6725807</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536392</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123536393</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>540883</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6725845</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536393</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123536395</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>540903</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6725820</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536395</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136797796</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>540614</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6725749</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797796</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136797800</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>540861</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6725879</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797800</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136797803</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>540855</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6725884</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797803</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136797804</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>540846</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6725883</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797804</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136797805</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>540842</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6725903</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797805</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136797806</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>540838</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6725897</v>
+      </c>
+      <c r="S78" t="n">
+        <v>11</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797806</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136797807</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lövängsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>540825</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6725899</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136797807</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123520461</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>540752</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6725524</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123520461</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123536377</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sundborn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>540675</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6725546</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536377</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>123520468</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>540656</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6725616</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123520468</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>123520537</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>540657</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6725618</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123520537</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>123522966</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lövängesberget, Lövängesberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>540693</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6725637</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123522966</t>
         </is>
@@ -8210,6 +10221,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>136797797</v>
       </c>
       <c r="B35" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -1960,11 +1960,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>
@@ -2644,11 +2640,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>
@@ -3169,11 +3161,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>
@@ -3286,11 +3274,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>
@@ -3403,11 +3387,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>
@@ -4371,11 +4351,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lövängsberget, Dlr</t>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>136797794</v>
       </c>
       <c r="B19" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136797795</v>
       </c>
       <c r="B24" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136797799</v>
       </c>
       <c r="B25" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>136797801</v>
       </c>
       <c r="B26" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>136797797</v>
       </c>
       <c r="B35" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34868-2026 artfynd.xlsx
+++ b/artfynd/A 34868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136797791</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136797792</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136797802</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136797790</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>136797798</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136797796</v>
       </c>
       <c r="B73" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>136797800</v>
       </c>
       <c r="B74" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>136797803</v>
       </c>
       <c r="B75" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136797804</v>
       </c>
       <c r="B76" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>136797805</v>
       </c>
       <c r="B77" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>136797806</v>
       </c>
       <c r="B78" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>136797807</v>
       </c>
       <c r="B79" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
